--- a/GameDesign/Excel/Equip.xlsx
+++ b/GameDesign/Excel/Equip.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,29 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +55,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,6 +167,46 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>장비 TID (종류×1000+순번 — 무기 1xxx · 장신구 2xxx · 보석 3xxx)</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>레어도 (전역 등급)</t>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>종류 (허용 칸을 정한다 — 장신구는 Accessory1·2 어디든)</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>대상 산업 (None=전 산업)</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>작업속도 가산 (천분율 · 250 = +25% · 기본값 기준)</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>기본 가격 (즉시 판매 기준 · 아직 미사용)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,415 +493,454 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>장비 TID (종류×1000+순번 — 무기 1xxx · 장신구 2xxx · 보석 3xxx)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>장비 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>레어도 (전역 등급)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>종류 (허용 칸을 정한다 — 장신구는 Accessory1·2 어디든)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>대상 산업 (None=전 산업)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>작업속도 가산 (천분율 · 250 = +25% · 기본값 기준)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>기본 가격 (즉시 판매 기준 · 아직 미사용)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>레어도</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>종류</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>대상 산업</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>속도 가산(‰)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>기본 가격</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>eGlobalRarity</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>eEquipKind</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n">
         <v>-999</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>EquipTID</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>GlobalRarity</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>EquipKind</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>SpeedAddPermille</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>BasePrice</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="5" t="n">
         <v>1001</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>목검</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>전 산업 +10% · 테스트값</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="5" t="n">
         <v>1002</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>낚싯대</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>낚시 +30% · 테스트값</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="5" t="n">
         <v>2001</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>구리 반지</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Accessory</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>전 산업 +5% · 테스트값</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="5" t="n">
         <v>2002</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>어부의 목걸이</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Accessory</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>낚시 +20% · 테스트값</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
+      <c r="B14" s="5" t="n">
         <v>3001</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>원석</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Gem</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>전 산업 +3% · 테스트값</t>
         </is>
@@ -824,5 +948,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Equip.xlsx
+++ b/GameDesign/Excel/Equip.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +33,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,8 +61,13 @@
         <fgColor theme="9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -69,11 +89,12 @@
         <color indexed="64"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,6 +113,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,435 +555,451 @@
     <col width="25" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="13" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="13" t="n"/>
+      <c r="I1" s="13" t="n"/>
+    </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>장비 TID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>레어도</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>종류</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>대상 산업</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>속도 가산(‰)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>기본 가격</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>eGlobalRarity</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>eEquipKind</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n">
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n">
         <v>-999</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="3" t="n"/>
+      <c r="I5" s="9" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>EquipTID</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>GlobalRarity</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>EquipKind</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>SpeedAddPermille</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>BasePrice</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="n">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="11" t="n">
         <v>1001</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>목검</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>전 산업 +10% · 테스트값</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="n">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="11" t="n">
         <v>1002</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>낚싯대</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="11" t="n">
         <v>120</v>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>낚시 +30% · 테스트값</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="5" t="n">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="11" t="n">
         <v>2001</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>구리 반지</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Accessory</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>전 산업 +5% · 테스트값</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="n">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="11" t="n">
         <v>2002</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>어부의 목걸이</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Accessory</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>낚시 +20% · 테스트값</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="5" t="n">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="11" t="n">
         <v>3001</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>원석</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Gem</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>전 산업 +3% · 테스트값</t>
         </is>

--- a/GameDesign/Excel/Equip.xlsx
+++ b/GameDesign/Excel/Equip.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="EquipTable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DisassembleTable" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -117,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -156,6 +157,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3497,4 +3504,306 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>재료</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>eGlobalRarity</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>ItemTable.ItemTID</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Rarity</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>ItemTID</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>ItemCount</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>100050</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>일반 장비 분해 → 마력의 파편 1개</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>100050</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>고급 장비 분해 → 마력의 파편 2개</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>100050</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>희귀 장비 분해 → 마력의 파편 5개</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>100050</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>영웅 장비 분해 → 마력의 파편 15개</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>100050</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>전설 장비 분해 → 마력의 파편 50개</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>100050</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>신화 장비 분해 → 마력의 파편 150개</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GameDesign/Excel/Equip.xlsx
+++ b/GameDesign/Excel/Equip.xlsx
@@ -567,7 +567,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="17" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="15" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="12" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="15" bestFit="1" customWidth="1" min="6" max="6"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>낚싯대</t>
+          <t>무쇠 삽</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G11" s="13" t="n">
@@ -942,7 +942,7 @@
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>낚시 +18% · 구 번호(낚시 무기 Uncommon 자리 — 1202는 결번)</t>
+          <t>발굴 +18% · 구 번호(발굴 무기 Uncommon 자리 — 1202는 결번)</t>
         </is>
       </c>
       <c r="J11" s="8" t="n"/>
@@ -992,7 +992,7 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>어부의 목걸이</t>
+          <t>탐험가의 목걸이</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G13" s="13" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>낚시 +18% · 구 번호(유일한 산업 전용 장신구)</t>
+          <t>발굴 +18% · 구 번호(유일한 산업 전용 장신구)</t>
         </is>
       </c>
       <c r="J13" s="8" t="n"/>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>대나무 낚싯대</t>
+          <t>나무 모종삽</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G21" s="13" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>낚시 +10%</t>
+          <t>발굴 +10%</t>
         </is>
       </c>
       <c r="J21" s="8" t="n"/>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>은사 낚싯대</t>
+          <t>강철 삽</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G22" s="13" t="n">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>낚시 +30%</t>
+          <t>발굴 +30%</t>
         </is>
       </c>
       <c r="J22" s="8" t="n"/>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>심해 작살</t>
+          <t>고고학자의 붓</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G23" s="13" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>낚시 +48%</t>
+          <t>발굴 +48%</t>
         </is>
       </c>
       <c r="J23" s="8" t="n"/>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>용린 낚싯대</t>
+          <t>용린 발굴삽</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G24" s="13" t="n">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>낚시 +72%</t>
+          <t>발굴 +72%</t>
         </is>
       </c>
       <c r="J24" s="8" t="n"/>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>해신의 삼지창</t>
+          <t>태초의 발굴삽</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G25" s="13" t="n">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>낚시 +100%</t>
+          <t>발굴 +100%</t>
         </is>
       </c>
       <c r="J25" s="8" t="n"/>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>물방울석</t>
+          <t>흙빛 조각석</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G55" s="13" t="n">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>낚시 +4%</t>
+          <t>발굴 +4%</t>
         </is>
       </c>
       <c r="J55" s="8" t="n"/>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>조류 수정</t>
+          <t>지층 수정</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G56" s="13" t="n">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>낚시 +7%</t>
+          <t>발굴 +7%</t>
         </is>
       </c>
       <c r="J56" s="8" t="n"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>심해의 청옥</t>
+          <t>유적의 호박</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G57" s="13" t="n">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>낚시 +12%</t>
+          <t>발굴 +12%</t>
         </is>
       </c>
       <c r="J57" s="8" t="n"/>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>산호 진주</t>
+          <t>고대 문양석</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G58" s="13" t="n">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>낚시 +19%</t>
+          <t>발굴 +19%</t>
         </is>
       </c>
       <c r="J58" s="8" t="n"/>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>바다의 심장</t>
+          <t>왕도의 심장</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G59" s="13" t="n">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>낚시 +29%</t>
+          <t>발굴 +29%</t>
         </is>
       </c>
       <c r="J59" s="8" t="n"/>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>해원의 성석</t>
+          <t>태고의 성석</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G60" s="13" t="n">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>낚시 +40%</t>
+          <t>발굴 +40%</t>
         </is>
       </c>
       <c r="J60" s="8" t="n"/>

--- a/GameDesign/Excel/Equip.xlsx
+++ b/GameDesign/Excel/Equip.xlsx
@@ -564,7 +564,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -713,42 +713,42 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
+          <t>lstring</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>eGlobalRarity</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>eEquipKind</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>eIndustryType</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>eGlobalRarity</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>eEquipKind</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>eIndustryType</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/GameDesign/Excel/Equip.xlsx
+++ b/GameDesign/Excel/Equip.xlsx
@@ -564,7 +564,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -3502,7 +3502,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3512,14 +3512,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3528,6 +3529,7 @@
       <c r="C1" s="8" t="n"/>
       <c r="D1" s="8" t="n"/>
       <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -3552,6 +3554,11 @@
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
+          <t>아티팩트 수량</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
           <t>메모</t>
         </is>
       </c>
@@ -3582,6 +3589,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -3605,6 +3617,11 @@
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -3623,7 +3640,10 @@
       <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="11" t="n"/>
+      <c r="E5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -3635,6 +3655,7 @@
       <c r="C6" s="11" t="n"/>
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -3645,7 +3666,8 @@
       <c r="B7" s="11" t="n"/>
       <c r="C7" s="11" t="n"/>
       <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -3665,6 +3687,7 @@
       </c>
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
@@ -3685,6 +3708,11 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
+          <t>ArtifactItemCount</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
           <t>Description</t>
         </is>
       </c>
@@ -3702,9 +3730,12 @@
       <c r="D10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>일반 장비 분해 → 마력의 파편 1개</t>
+      <c r="E10" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>일반 분해 → 마력의 파편 · 장비 1개 · 아티팩트 2개</t>
         </is>
       </c>
     </row>
@@ -3721,9 +3752,12 @@
       <c r="D11" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>고급 장비 분해 → 마력의 파편 2개</t>
+      <c r="E11" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>고급 분해 → 마력의 파편 · 장비 2개 · 아티팩트 4개</t>
         </is>
       </c>
     </row>
@@ -3740,9 +3774,12 @@
       <c r="D12" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>희귀 장비 분해 → 마력의 파편 5개</t>
+      <c r="E12" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>희귀 분해 → 마력의 파편 · 장비 5개 · 아티팩트 10개</t>
         </is>
       </c>
     </row>
@@ -3759,9 +3796,12 @@
       <c r="D13" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>영웅 장비 분해 → 마력의 파편 15개</t>
+      <c r="E13" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>영웅 분해 → 마력의 파편 · 장비 15개 · 아티팩트 30개</t>
         </is>
       </c>
     </row>
@@ -3778,9 +3818,12 @@
       <c r="D14" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>전설 장비 분해 → 마력의 파편 50개</t>
+      <c r="E14" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>전설 분해 → 마력의 파편 · 장비 50개 · 아티팩트 100개</t>
         </is>
       </c>
     </row>
@@ -3797,9 +3840,12 @@
       <c r="D15" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>신화 장비 분해 → 마력의 파편 150개</t>
+      <c r="E15" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>신화 분해 → 마력의 파편 · 장비 150개 · 아티팩트 300개</t>
         </is>
       </c>
     </row>
